--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:53</t>
+    <t xml:space="preserve">2026-08-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:05</t>
+    <t xml:space="preserve">2026-08-17 21:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:45</t>
+    <t xml:space="preserve">2026-09-06 20:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
